--- a/activity_sports_waivers_forms/005_surf_school_liability_waiver--activity_sports_waivers_forms.xlsx
+++ b/activity_sports_waivers_forms/005_surf_school_liability_waiver--activity_sports_waivers_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Parent Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Emergency Contact Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Relationship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Phone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Contact Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Instructor Name</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Instructor Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Instructor Email</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
